--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120164981</v>
+        <v>120164982</v>
       </c>
       <c r="B3" t="n">
-        <v>90582</v>
+        <v>90966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,7 +840,7 @@
         <v>6526752</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164982</v>
+        <v>120164981</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>90582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,7 +955,7 @@
         <v>6526752</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164980</v>
+        <v>120164987</v>
       </c>
       <c r="B5" t="n">
-        <v>90582</v>
+        <v>100171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,30 +1033,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598071</v>
+        <v>597960</v>
       </c>
       <c r="R5" t="n">
-        <v>6526753</v>
+        <v>6527014</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1099,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164987</v>
+        <v>120164980</v>
       </c>
       <c r="B6" t="n">
-        <v>100171</v>
+        <v>90582</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,31 +1149,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597960</v>
+        <v>598071</v>
       </c>
       <c r="R6" t="n">
-        <v>6527014</v>
+        <v>6526753</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120164992</v>
+        <v>120164987</v>
       </c>
       <c r="B2" t="n">
-        <v>105564</v>
+        <v>100171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -906,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164981</v>
+        <v>120164980</v>
       </c>
       <c r="B4" t="n">
         <v>90582</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598068</v>
+        <v>598071</v>
       </c>
       <c r="R4" t="n">
-        <v>6526752</v>
+        <v>6526753</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164987</v>
+        <v>120164992</v>
       </c>
       <c r="B5" t="n">
-        <v>100171</v>
+        <v>105564</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164980</v>
+        <v>120164981</v>
       </c>
       <c r="B6" t="n">
         <v>90582</v>
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598071</v>
+        <v>598068</v>
       </c>
       <c r="R6" t="n">
-        <v>6526753</v>
+        <v>6526752</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120164987</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120164982</v>
+        <v>120164984</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,26 +807,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598068</v>
+        <v>598156</v>
       </c>
       <c r="R3" t="n">
-        <v>6526752</v>
+        <v>6526703</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164980</v>
+        <v>120164982</v>
       </c>
       <c r="B4" t="n">
-        <v>90582</v>
+        <v>90984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598071</v>
+        <v>598068</v>
       </c>
       <c r="R4" t="n">
-        <v>6526753</v>
+        <v>6526752</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -984,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164992</v>
+        <v>120164980</v>
       </c>
       <c r="B5" t="n">
-        <v>105564</v>
+        <v>90600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1034,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597960</v>
+        <v>598071</v>
       </c>
       <c r="R5" t="n">
-        <v>6527014</v>
+        <v>6526753</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164981</v>
+        <v>120164992</v>
       </c>
       <c r="B6" t="n">
-        <v>90582</v>
+        <v>105588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,30 +1149,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R6" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120164984</v>
+        <v>120164981</v>
       </c>
       <c r="B7" t="n">
-        <v>100171</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,31 +1265,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598156</v>
+        <v>598068</v>
       </c>
       <c r="R7" t="n">
-        <v>6526703</v>
+        <v>6526752</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120164987</v>
+        <v>120164984</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597960</v>
+        <v>598156</v>
       </c>
       <c r="R2" t="n">
-        <v>6527014</v>
+        <v>6526703</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120164984</v>
+        <v>120164980</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598156</v>
+        <v>598071</v>
       </c>
       <c r="R3" t="n">
-        <v>6526703</v>
+        <v>6526753</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164982</v>
+        <v>120164987</v>
       </c>
       <c r="B4" t="n">
-        <v>90984</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,26 +922,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R4" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164980</v>
+        <v>120164981</v>
       </c>
       <c r="B5" t="n">
         <v>90600</v>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598071</v>
+        <v>598068</v>
       </c>
       <c r="R5" t="n">
-        <v>6526753</v>
+        <v>6526752</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164992</v>
+        <v>120164982</v>
       </c>
       <c r="B6" t="n">
-        <v>105588</v>
+        <v>90984</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,31 +1149,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597960</v>
+        <v>598068</v>
       </c>
       <c r="R6" t="n">
-        <v>6527014</v>
+        <v>6526752</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1216,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120164981</v>
+        <v>120164992</v>
       </c>
       <c r="B7" t="n">
-        <v>90600</v>
+        <v>105588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,30 +1264,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R7" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120164984</v>
+        <v>120164987</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598156</v>
+        <v>597960</v>
       </c>
       <c r="R2" t="n">
-        <v>6526703</v>
+        <v>6527014</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164987</v>
+        <v>120164982</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>90984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,27 +922,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597960</v>
+        <v>598068</v>
       </c>
       <c r="R4" t="n">
-        <v>6527014</v>
+        <v>6526752</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -985,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164981</v>
+        <v>120164992</v>
       </c>
       <c r="B5" t="n">
-        <v>90600</v>
+        <v>105588</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,30 +1033,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R5" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164982</v>
+        <v>120164981</v>
       </c>
       <c r="B6" t="n">
-        <v>90984</v>
+        <v>90600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,25 +1149,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
         <v>6526752</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120164992</v>
+        <v>120164984</v>
       </c>
       <c r="B7" t="n">
-        <v>105588</v>
+        <v>100194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,25 +1264,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597960</v>
+        <v>598156</v>
       </c>
       <c r="R7" t="n">
-        <v>6527014</v>
+        <v>6526703</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164982</v>
+        <v>120164992</v>
       </c>
       <c r="B4" t="n">
-        <v>90984</v>
+        <v>105588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,30 +918,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R4" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -984,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164992</v>
+        <v>120164982</v>
       </c>
       <c r="B5" t="n">
-        <v>105588</v>
+        <v>90984</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1034,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597960</v>
+        <v>598068</v>
       </c>
       <c r="R5" t="n">
-        <v>6527014</v>
+        <v>6526752</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120164987</v>
+        <v>120164984</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597960</v>
+        <v>598156</v>
       </c>
       <c r="R2" t="n">
-        <v>6527014</v>
+        <v>6526703</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164992</v>
+        <v>120164987</v>
       </c>
       <c r="B4" t="n">
-        <v>105588</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164982</v>
+        <v>120164981</v>
       </c>
       <c r="B5" t="n">
-        <v>90984</v>
+        <v>90600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,25 +1034,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
         <v>6526752</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164981</v>
+        <v>120164992</v>
       </c>
       <c r="B6" t="n">
-        <v>90600</v>
+        <v>105588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,30 +1149,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R6" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120164984</v>
+        <v>120164982</v>
       </c>
       <c r="B7" t="n">
-        <v>100194</v>
+        <v>90984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,27 +1269,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598156</v>
+        <v>598068</v>
       </c>
       <c r="R7" t="n">
-        <v>6526703</v>
+        <v>6526752</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120164984</v>
+        <v>120164980</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598156</v>
+        <v>598071</v>
       </c>
       <c r="R2" t="n">
-        <v>6526703</v>
+        <v>6526753</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120164980</v>
+        <v>120164984</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,30 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598071</v>
+        <v>598156</v>
       </c>
       <c r="R3" t="n">
-        <v>6526753</v>
+        <v>6526703</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164981</v>
+        <v>120164982</v>
       </c>
       <c r="B5" t="n">
-        <v>90600</v>
+        <v>90984</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,25 +1034,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
         <v>6526752</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164992</v>
+        <v>120164981</v>
       </c>
       <c r="B6" t="n">
-        <v>105588</v>
+        <v>90600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,31 +1149,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597960</v>
+        <v>598068</v>
       </c>
       <c r="R6" t="n">
-        <v>6527014</v>
+        <v>6526752</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120164982</v>
+        <v>120164992</v>
       </c>
       <c r="B7" t="n">
-        <v>90984</v>
+        <v>105588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,30 +1264,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R7" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120164980</v>
+        <v>120164987</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598071</v>
+        <v>597960</v>
       </c>
       <c r="R2" t="n">
-        <v>6526753</v>
+        <v>6527014</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120164984</v>
+        <v>120164980</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +803,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598156</v>
+        <v>598071</v>
       </c>
       <c r="R3" t="n">
-        <v>6526703</v>
+        <v>6526753</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164987</v>
+        <v>120164984</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597960</v>
+        <v>598156</v>
       </c>
       <c r="R4" t="n">
-        <v>6527014</v>
+        <v>6526703</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164981</v>
+        <v>120164992</v>
       </c>
       <c r="B6" t="n">
-        <v>90600</v>
+        <v>105588</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,30 +1149,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R6" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120164992</v>
+        <v>120164981</v>
       </c>
       <c r="B7" t="n">
-        <v>105588</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,31 +1265,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597960</v>
+        <v>598068</v>
       </c>
       <c r="R7" t="n">
-        <v>6527014</v>
+        <v>6526752</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38456-2024 artfynd.xlsx
+++ b/artfynd/A 38456-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120164987</v>
+        <v>120164984</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597960</v>
+        <v>598156</v>
       </c>
       <c r="R2" t="n">
-        <v>6527014</v>
+        <v>6526703</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120164984</v>
+        <v>120164992</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>105588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598156</v>
+        <v>597960</v>
       </c>
       <c r="R4" t="n">
-        <v>6526703</v>
+        <v>6527014</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120164982</v>
+        <v>120164987</v>
       </c>
       <c r="B5" t="n">
-        <v>90984</v>
+        <v>100194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,26 +1038,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598068</v>
+        <v>597960</v>
       </c>
       <c r="R5" t="n">
-        <v>6526752</v>
+        <v>6527014</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120164992</v>
+        <v>120164981</v>
       </c>
       <c r="B6" t="n">
-        <v>105588</v>
+        <v>90600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,31 +1150,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597960</v>
+        <v>598068</v>
       </c>
       <c r="R6" t="n">
-        <v>6527014</v>
+        <v>6526752</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120164981</v>
+        <v>120164982</v>
       </c>
       <c r="B7" t="n">
-        <v>90600</v>
+        <v>90984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
         <v>6526752</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
